--- a/reports/scan/fs_medical_clinic_fs.xlsx
+++ b/reports/scan/fs_medical_clinic_fs.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -622,9 +622,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -637,9 +637,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -699,9 +699,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -714,9 +714,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -768,57 +768,57 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -845,57 +845,57 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -917,72 +917,72 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1099,9 +1099,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1176,9 +1176,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1201,9 +1201,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1253,9 +1253,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1315,9 +1315,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1330,9 +1330,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1407,9 +1407,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1484,9 +1484,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1561,29 +1561,29 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>36</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1705,39 +1705,39 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>48</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1966,9 +1966,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>36</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2090,16 +2090,16 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2120,9 +2120,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/reports/scan/fs_medical_clinic_fs.xlsx
+++ b/reports/scan/fs_medical_clinic_fs.xlsx
@@ -51,12 +51,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCC99"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -532,72 +532,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -657,7 +657,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -706,14 +706,14 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -734,9 +734,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -768,57 +768,57 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -845,30 +845,30 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -888,14 +888,14 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -917,72 +917,72 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1007,22 +1007,22 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1042,7 +1042,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1071,72 +1071,72 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1148,72 +1148,72 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1225,62 +1225,62 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1315,17 +1315,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1350,7 +1350,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1397,12 +1397,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1427,7 +1427,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1474,12 +1474,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1504,7 +1504,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1551,19 +1551,19 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1581,7 +1581,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -1608,74 +1608,74 @@
           <t>patients/</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1685,74 +1685,74 @@
           <t>patients/alice_johnson/</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1762,74 +1762,74 @@
           <t>patients/bob_martinez/</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1839,72 +1839,72 @@
           <t>billing/</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1916,72 +1916,72 @@
           <t>billing/invoices/</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2013,14 +2013,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -2070,72 +2070,72 @@
           <t>policies/</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">

--- a/reports/scan/fs_medical_clinic_fs.xlsx
+++ b/reports/scan/fs_medical_clinic_fs.xlsx
@@ -51,12 +51,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCC99"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -629,14 +629,14 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
           <t>24</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -657,9 +657,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
           <t>24</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -734,9 +734,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -781,17 +781,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -811,7 +811,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -855,24 +855,24 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -888,7 +888,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -935,17 +935,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -965,7 +965,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1012,17 +1012,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1042,7 +1042,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1086,24 +1086,24 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1119,7 +1119,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1166,17 +1166,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1196,7 +1196,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1243,12 +1243,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1273,7 +1273,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1320,12 +1320,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1350,7 +1350,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1397,12 +1397,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1427,7 +1427,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1474,12 +1474,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1504,7 +1504,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -1551,14 +1551,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1581,7 +1581,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -1608,72 +1608,72 @@
           <t>patients/</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1685,72 +1685,72 @@
           <t>patients/alice_johnson/</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1762,72 +1762,72 @@
           <t>patients/bob_martinez/</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1839,32 +1839,32 @@
           <t>billing/</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1874,37 +1874,37 @@
           <t>16</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1916,32 +1916,32 @@
           <t>billing/invoices/</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1951,37 +1951,37 @@
           <t>16</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2013,14 +2013,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -2070,34 +2070,34 @@
           <t>policies/</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2105,37 +2105,37 @@
           <t>16</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
